--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486668_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486668_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3378</v>
+        <v>2.8136</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8929</v>
+        <v>3.7413</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5552</v>
+        <v>-0.9276</v>
       </c>
       <c r="G2" t="n">
         <v>3.3894</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4966</v>
+        <v>-0.0276</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4971</v>
+        <v>-0.6488</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9937</v>
+        <v>0.6212</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5482</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3418</v>
+        <v>1.6634</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3317</v>
+        <v>1.5043</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0101</v>
+        <v>0.1591</v>
       </c>
       <c r="G3" t="n">
         <v>1.483</v>
@@ -688,13 +688,13 @@
         <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6231</v>
+        <v>-0.0552</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7995</v>
+        <v>-0.0279</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1763</v>
+        <v>-0.0274</v>
       </c>
       <c r="V3" t="n">
         <v>0.0426</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4229</v>
+        <v>0.3758</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3365</v>
+        <v>0.1876</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7593</v>
+        <v>0.1882</v>
       </c>
       <c r="G4" t="n">
         <v>-2.2207</v>
@@ -766,13 +766,13 @@
         <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1598</v>
+        <v>-0.2069</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5729</v>
+        <v>-1.0488</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4131</v>
+        <v>0.8419</v>
       </c>
       <c r="V4" t="n">
         <v>0.6795</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6375</v>
+        <v>-0.1768</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.39</v>
+        <v>-1.128</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.9512</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7146</v>
@@ -844,13 +844,13 @@
         <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6952</v>
+        <v>-0.2345</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5518</v>
+        <v>-0.2898</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1434</v>
+        <v>0.0553</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.5645</v>
+        <v>-1.8762</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4272</v>
+        <v>-0.0617</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1373</v>
+        <v>-1.8145</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0148</v>
@@ -922,13 +922,13 @@
         <v>1.7377</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5227</v>
+        <v>-0.8345</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1866</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3361</v>
+        <v>-0.0133</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8338</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9603</v>
+        <v>-2.9326</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.5404</v>
+        <v>-3.6369</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.7043</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9964</v>
@@ -1000,13 +1000,13 @@
         <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1381</v>
+        <v>-0.1104</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2212</v>
+        <v>-0.3177</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.2073</v>
       </c>
       <c r="V7" t="n">
         <v>-1.405</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2877</v>
+        <v>-3.4505</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0919</v>
+        <v>-2.9815</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1958</v>
+        <v>-0.469</v>
       </c>
       <c r="G8" t="n">
         <v>-3.3822</v>
@@ -1078,13 +1078,13 @@
         <v>0.3862</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1215</v>
+        <v>-0.0413</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8002</v>
+        <v>-0.6898</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9217</v>
+        <v>0.6485</v>
       </c>
       <c r="V8" t="n">
         <v>-0.22</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6744</v>
+        <v>-3.8868</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4512</v>
+        <v>-3.0858</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2232</v>
+        <v>-0.801</v>
       </c>
       <c r="G9" t="n">
         <v>-4.7489</v>
@@ -1156,13 +1156,13 @@
         <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3463</v>
+        <v>-0.5587</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0761</v>
+        <v>-0.7107</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2702</v>
+        <v>0.152</v>
       </c>
       <c r="V9" t="n">
         <v>1.2277</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.021899999999999</v>
+        <v>-7.4701</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.012599999999999</v>
+        <v>-5.460699999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.009500000000001</v>
+        <v>-2.0093</v>
       </c>
       <c r="G10" t="n">
         <v>-8.2052</v>
@@ -1234,13 +1234,13 @@
         <v>11.5847</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.6209</v>
+        <v>-2.0691</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.106400000000001</v>
+        <v>-4.5546</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4856</v>
+        <v>2.4855</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0572</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.2675</v>
+        <v>5.4399</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7652</v>
+        <v>3.6618</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5024</v>
+        <v>1.7781</v>
       </c>
       <c r="G11" t="n">
         <v>2.6055</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2759</v>
+        <v>0.4483</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2486</v>
+        <v>-0.352</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5245</v>
+        <v>0.8003</v>
       </c>
       <c r="V11" t="n">
         <v>1.2277</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BOONYASITH</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7378</v>
+        <v>3.2641</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3915</v>
+        <v>1.3052</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3463</v>
+        <v>1.9589</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6713</v>
+        <v>1.642</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2967</v>
+        <v>-0.0422</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6254</v>
+        <v>1.6842</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8521</v>
+        <v>1.5536</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9182</v>
+        <v>0.1655</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0662</v>
+        <v>1.3881</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1808</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.2077</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4408</v>
+        <v>0.2961</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9308</v>
+        <v>-0.1931</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="S12" t="n">
-        <v>0.982</v>
+        <v>0.9656</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3857</v>
+        <v>-0.0554</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5963000000000001</v>
+        <v>1.021</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8568</v>
+        <v>0.6565</v>
       </c>
       <c r="W12" t="n">
-        <v>2.0845</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2277</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>J. BOONYASITH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.685</v>
+        <v>2.4317</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8915</v>
+        <v>1.771</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7935</v>
+        <v>0.6607</v>
       </c>
       <c r="G13" t="n">
-        <v>1.642</v>
+        <v>1.6713</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0422</v>
+        <v>3.2967</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6842</v>
+        <v>-1.6254</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5536</v>
+        <v>1.8521</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1655</v>
+        <v>3.9182</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3881</v>
+        <v>-2.0662</v>
       </c>
       <c r="M13" t="n">
-        <v>0.08840000000000001</v>
+        <v>-0.1808</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2077</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2961</v>
+        <v>0.4408</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1931</v>
+        <v>-1.9308</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3865</v>
+        <v>0.6758</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4691</v>
+        <v>-0.2349</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8556</v>
+        <v>0.9107</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6565</v>
+        <v>0.8568</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.0845</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6565</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3123</v>
+        <v>0.9565</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.222</v>
+        <v>-0.4288</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5343</v>
+        <v>1.3853</v>
       </c>
       <c r="G14" t="n">
         <v>0.883</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4799</v>
+        <v>0.1241</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3038</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7837</v>
+        <v>0.6347</v>
       </c>
       <c r="V14" t="n">
         <v>0.5286</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2195</v>
+        <v>0.5597</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2023</v>
+        <v>1.7194</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4218</v>
+        <v>-1.1597</v>
       </c>
       <c r="G15" t="n">
         <v>2.1914</v>
@@ -1624,13 +1624,13 @@
         <v>0.3862</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0827</v>
+        <v>0.6965</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5795</v>
+        <v>-0.0624</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4968</v>
+        <v>0.7589</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5559</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3971</v>
+        <v>0.4455</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8149</v>
+        <v>-0.2978</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4178</v>
+        <v>0.7433</v>
       </c>
       <c r="G16" t="n">
         <v>1.1285</v>
@@ -1702,13 +1702,13 @@
         <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.1585</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2417</v>
+        <v>-0.7245</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5576</v>
+        <v>0.8831</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2277</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4629</v>
+        <v>-0.4132</v>
       </c>
       <c r="E17" t="n">
         <v>-0.09569999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3672</v>
+        <v>-0.3176</v>
       </c>
       <c r="G17" t="n">
         <v>0.2005</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0496</v>
+        <v>0.0001</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1711</v>
+        <v>0.2208</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6138</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4446</v>
+        <v>-0.886</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4034</v>
+        <v>-3.4983</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0411</v>
+        <v>2.6123</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0802</v>
+        <v>-1.0368</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8067</v>
+        <v>-2.6622</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2735</v>
+        <v>1.6254</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1969</v>
+        <v>-1.4695</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4611</v>
+        <v>-2.2473</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6579</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.277</v>
+        <v>0.4327</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3456</v>
+        <v>-0.4149</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9314</v>
+        <v>0.8477</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1239</v>
+        <v>-3.0892</v>
       </c>
       <c r="R18" t="n">
         <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7941</v>
+        <v>1.0896</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5236</v>
+        <v>-0.1246</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2705</v>
+        <v>1.2142</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1851</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1851</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4569</v>
+        <v>-1.7078</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7052</v>
+        <v>-2.1274</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2483</v>
+        <v>0.4196</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0368</v>
+        <v>-1.0802</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6622</v>
+        <v>-0.8067</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6254</v>
+        <v>-0.2735</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4695</v>
+        <v>0.1969</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.2473</v>
+        <v>-0.4611</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.6579</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4327</v>
+        <v>-1.277</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4149</v>
+        <v>-0.3456</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8477</v>
+        <v>-0.9314</v>
       </c>
       <c r="P19" t="n">
+        <v>-1.1585</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-2.1239</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-3.0892</v>
       </c>
       <c r="R19" t="n">
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5187</v>
+        <v>0.5308</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3314</v>
+        <v>-0.2004</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8502</v>
+        <v>0.7312</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1851</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1851</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,19 +1969,19 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>8.021599999999999</v>
+        <v>10.0904</v>
       </c>
       <c r="E20" t="n">
-        <v>2.009300000000001</v>
+        <v>2.0094</v>
       </c>
       <c r="F20" t="n">
-        <v>6.012499999999999</v>
+        <v>8.0809</v>
       </c>
       <c r="G20" t="n">
         <v>8.2052</v>
       </c>
       <c r="H20" t="n">
-        <v>2.757</v>
+        <v>2.757000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>5.4482</v>
@@ -1990,7 +1990,7 @@
         <v>10.7681</v>
       </c>
       <c r="K20" t="n">
-        <v>6.212199999999998</v>
+        <v>6.212200000000001</v>
       </c>
       <c r="L20" t="n">
         <v>4.5556</v>
@@ -2014,13 +2014,13 @@
         <v>7.7232</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6208</v>
+        <v>4.6893</v>
       </c>
       <c r="T20" t="n">
         <v>-2.4855</v>
       </c>
       <c r="U20" t="n">
-        <v>5.1063</v>
+        <v>7.1749</v>
       </c>
       <c r="V20" t="n">
         <v>1.0573</v>
